--- a/education_surveys/025_public_awareness_of_human_trafficking_survey--education_surveys.xlsx
+++ b/education_surveys/025_public_awareness_of_human_trafficking_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>page_1</t>
+          <t>human_trafficking_awareness</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>human_trafficking_survey</t>
+          <t>What do you know about human trafficking?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>demographic_info</t>
+          <t>level_of_knowledge</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>demographic_info</t>
+          <t>How much do you know about human trafficking?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>awareness_question_1</t>
+          <t>human_trafficking_heard</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>what_do_you_know_about_human_trafficking</t>
+          <t>Have you ever heard of human trafficking before?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>awareness_question_2</t>
+          <t>risks_associated</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>what_do_you_know_about_human_trafficking</t>
+          <t>What are the risks associated with human trafficking?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>awareness_question_3</t>
+          <t>prevention_methods</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>what_do_you_know_about_human_trafficking</t>
+          <t>How can human trafficking be prevented?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>awareness_question_4</t>
+          <t>awareness_raising</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>what_do_you_know_about_human_trafficking</t>
+          <t>What can be done to raise awareness about human trafficking?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>awareness_question_5</t>
+          <t>human_traffacking_info</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>what_do_you_know_about_human_trafficking</t>
+          <t>Have you ever come across any information about human trafficking?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>awareness_question_6</t>
+          <t>level_of_concern</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>what_do_you_know_about_human_traffacking</t>
+          <t>What is your level of concern about human trafficking?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>awareness_question_7</t>
+          <t>prevention_effectiveness</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>what_do_you_know_about_human_trafficking</t>
+          <t>What do you think is the most effective way to prevent human trafficking?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>awareness_question_8</t>
+          <t>knowledge_rating</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>what_do_you_know_about_human_traffacking</t>
+          <t>How would you rate your knowledge about human trafficking on a scale of 1-5?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>awareness_question_9</t>
+          <t>human_traffacking_types</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>what_do_you_know_about_human_traffacking</t>
+          <t>What is your understanding of the difference between human trafficking and smuggling?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>awareness_question_10</t>
+          <t>educate_about_human_traffacking</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>what_do_you_know_about_human_traffacking</t>
+          <t>How can people be educated about human trafficking?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>awareness_question_11</t>
+          <t>human_traffacking_experience</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>what_do_you_know_about_human_traffacking</t>
+          <t>Have you ever been affected by human trafficking or know someone who has?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>awareness_question_12</t>
+          <t>common_cases</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>what_do_you_know_about_human_traffacking</t>
+          <t>What are the most common types of human trafficking cases?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>awareness_question_13</t>
+          <t>consequences_of_human_traffacking</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>what_do_you_know_about_human_traffacking</t>
+          <t>What are the consequences of human trafficking?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>awareness_question_14</t>
+          <t>community_prevention</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>awareness_question_14</t>
+          <t>How can communities come together to prevent human trafficking?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>awareness_question_15</t>
+          <t>government_role</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>awareness_question_15</t>
+          <t>What role do you think the government should play in preventing human trafficking?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>awareness_question_16</t>
+          <t>awareness_question_17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>awareness_question_16</t>
+          <t>Awareness Question 17</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>awareness_question_17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>awareness_question_17</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>awareness_question_18</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>awareness_question_18</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>awareness_question_19</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>awareness_question_19</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>awareness_question_20</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>awareness_question_20</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>awareness_question_21</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>awareness_question_21</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>awareness_question_22</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>awareness_question_22</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>awareness_question_23</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>awareness_question_23</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,952 +965,408 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>awareness_question_1_choices</t>
+          <t>level_of_knowledge_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>awareness_question_1_choices</t>
+          <t>level_of_knowledge_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>awareness_question_1_choices</t>
+          <t>level_of_knowledge_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>awareness_question_1_choices</t>
+          <t>level_of_knowledge_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>awareness_question_2_choices</t>
+          <t>prevention_methods_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>awareness_question_2_choices</t>
+          <t>prevention_methods_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>awareness_question_2_choices</t>
+          <t>prevention_methods_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>awareness_question_2_choices</t>
+          <t>prevention_methods_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>awareness_question_3_choices</t>
+          <t>awareness_raising_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>awareness_question_3_choices</t>
+          <t>awareness_raising_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>awareness_question_3_choices</t>
+          <t>awareness_raising_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>awareness_question_3_choices</t>
+          <t>awareness_raising_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>awareness_question_4_choices</t>
+          <t>level_of_concern_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>awareness_question_4_choices</t>
+          <t>level_of_concern_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>awareness_question_4_choices</t>
+          <t>level_of_concern_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>awareness_question_4_choices</t>
+          <t>level_of_concern_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>awareness_question_5_choices</t>
+          <t>prevention_effectiveness_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>awareness_question_5_choices</t>
+          <t>prevention_effectiveness_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>awareness_question_5_choices</t>
+          <t>prevention_effectiveness_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>awareness_question_5_choices</t>
+          <t>prevention_effectiveness_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>awareness_question_6_choices</t>
+          <t>community_prevention_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>awareness_question_6_choices</t>
+          <t>community_prevention_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>awareness_question_6_choices</t>
+          <t>community_prevention_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>awareness_question_6_choices</t>
+          <t>community_prevention_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option4</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>awareness_question_7_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>awareness_question_7_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>awareness_question_7_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>awareness_question_7_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>awareness_question_8_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>awareness_question_8_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>awareness_question_8_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>awareness_question_8_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>awareness_question_9_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>awareness_question_9_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>awareness_question_9_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>awareness_question_9_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>awareness_question_10_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>awareness_question_10_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>awareness_question_10_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>awareness_question_10_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>awareness_question_11_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>awareness_question_11_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>awareness_question_11_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>awareness_question_11_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>awareness_question_12_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>awareness_question_12_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>awareness_question_12_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>awareness_question_12_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>awareness_question_13_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>awareness_question_13_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>awareness_question_18_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>awareness_question_18_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>awareness_question_18_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>awareness_question_18_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>awareness_question_19_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>awareness_question_19_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
